--- a/output/pdf_financials_xlsx/ABC.xlsx
+++ b/output/pdf_financials_xlsx/ABC.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.846197</v>
+        <v>-0.846197</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>13.722752</v>
+        <v>-13.722752</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>10.395944</v>
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.846197</v>
+        <v>-0.846197</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13.722752</v>
+        <v>-13.722752</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>10.395944</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.846197</v>
+        <v>-0.846197</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>13.722752</v>
+        <v>-13.722752</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>10.395944</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10.577462</v>
+        <v>-10.577462</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>11.066735</v>
+        <v>-11.066735</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.846197</v>
+        <v>-0.846197</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>13.722752</v>
+        <v>-13.722752</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>10.395944</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.853563</v>
+        <v>-0.838831</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13.729073</v>
+        <v>-13.716431</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>10.395944</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.242125</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.249876</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.350647</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.350647</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>10.395944</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.660381</v>
+        <v>-0.660381</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.606502</v>
@@ -4567,7 +4567,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -5182,7 +5186,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>4.242125</v>
       </c>
@@ -5367,7 +5375,7 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.660381</v>
+        <v>-0.660381</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>-0.606502</v>
@@ -9600,10 +9608,10 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0.846197</v>
+        <v>-0.846197</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>13.722752</v>
+        <v>-13.722752</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9682,10 +9690,10 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0.431767</v>
+        <v>-0.431767</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>13.155846</v>
+        <v>-13.155846</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ABC.xlsx
+++ b/output/pdf_financials_xlsx/ABC.xlsx
@@ -687,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035567</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.034458</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>-13.722752</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>10.395944</v>
+        <v>10.431511</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.660381</v>
+        <v>0.694839</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.606502</v>
@@ -1087,10 +1087,10 @@
         <v>-13.716431</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10.395944</v>
+        <v>10.431511</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.660381</v>
+        <v>0.694839</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.606502</v>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003925</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.046786</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>2.774022</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.003925</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.046786</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>2.774022</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.003996</v>
+        <v>7.1e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.046857</v>
+        <v>7.1e-05</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">

--- a/output/pdf_financials_xlsx/ABC.xlsx
+++ b/output/pdf_financials_xlsx/ABC.xlsx
@@ -1932,16 +1932,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.296385</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.116115</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.006436</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.025744</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -6938,7 +6938,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>0.006436</v>
       </c>
